--- a/株式会社慈久庵/【慈久庵】案件マスター.xlsx
+++ b/株式会社慈久庵/【慈久庵】案件マスター.xlsx
@@ -121,6 +121,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">期目</t>
     </r>
@@ -144,6 +145,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">期目</t>
     </r>
@@ -167,6 +169,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">期目</t>
     </r>
@@ -196,6 +199,7 @@
         <color theme="0"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -217,6 +221,7 @@
         <color theme="0"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期</t>
     </r>
@@ -240,6 +245,7 @@
         <color theme="0"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -261,6 +267,7 @@
         <color theme="0"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期</t>
     </r>
@@ -284,6 +291,7 @@
         <color theme="0"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -305,6 +313,7 @@
         <color theme="0"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期</t>
     </r>
@@ -396,6 +405,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">単位：千円</t>
     </r>
@@ -556,6 +566,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">に貼るときは非表示→</t>
     </r>
@@ -652,6 +663,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">に貼るときは非表示</t>
     </r>
@@ -717,6 +729,7 @@
         <color rgb="FFC03A2B"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">（株式価値評価）パート　※本案件では未着手です。以下のシートはテンプレートの初期値（ダミー値）のままであり、評価書の作成時に更新してください。修正</t>
     </r>
@@ -738,6 +751,7 @@
         <color rgb="FFC03A2B"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・修正</t>
     </r>
@@ -759,6 +773,7 @@
         <color rgb="FFC03A2B"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・年買法・</t>
     </r>
@@ -780,6 +795,7 @@
         <color rgb="FFC03A2B"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">マルチプル・参照企業の各シートの数値は本案件の実績値ではありません。</t>
     </r>
@@ -975,6 +991,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">日</t>
     </r>
@@ -994,6 +1011,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">日</t>
     </r>
@@ -1030,6 +1048,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -1051,6 +1070,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">か月</t>
     </r>
@@ -1258,6 +1278,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">（</t>
     </r>
@@ -1277,6 +1298,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">倍率）</t>
     </r>
@@ -1321,6 +1343,7 @@
         <color theme="0"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">倍率</t>
     </r>
@@ -1377,6 +1400,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -1394,6 +1418,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -1411,6 +1436,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">日設立（第</t>
     </r>
@@ -1428,6 +1454,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">期）
 ※</t>
@@ -1446,6 +1473,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年に東京・南阿佐ヶ谷で石臼挽き自家製粉の手打ち蕎麦店「慈久庵」を開業（法人設立と同年）。</t>
     </r>
@@ -1463,6 +1491,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年に代表者の生まれ故郷である茨城県久慈郡水府村（現・常陸太田市）へ移転し、現店舗で営業</t>
     </r>
@@ -1484,6 +1513,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">千円</t>
     </r>
@@ -1527,6 +1557,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">名（</t>
     </r>
@@ -1546,6 +1577,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -1565,6 +1597,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -1584,6 +1617,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">日時点）
 ※代表者・配偶者の</t>
@@ -1604,6 +1638,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">名で運営。繁忙時は親族が就労（</t>
     </r>
@@ -1623,6 +1658,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -1642,6 +1678,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期 雑給 </t>
     </r>
@@ -1661,6 +1698,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">千円）</t>
     </r>
@@ -1689,6 +1727,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">千円（</t>
     </r>
@@ -1708,6 +1747,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -1727,6 +1767,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期）</t>
     </r>
@@ -1751,6 +1792,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">千円（</t>
     </r>
@@ -1770,6 +1812,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -1789,6 +1832,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期）
 ※営業利益△</t>
@@ -1809,6 +1853,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">千円＋減価償却費</t>
     </r>
@@ -1828,6 +1873,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">千円。</t>
     </r>
@@ -1847,6 +1893,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">上の調整項目なし</t>
     </r>
@@ -1935,6 +1982,7 @@
         <color theme="0"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -1954,6 +2002,7 @@
         <color theme="0"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期</t>
     </r>
@@ -1975,6 +2024,7 @@
         <color theme="0"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -1994,6 +2044,7 @@
         <color theme="0"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期</t>
     </r>
@@ -2015,6 +2066,7 @@
         <color theme="0"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -2034,6 +2086,7 @@
         <color theme="0"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期</t>
     </r>
@@ -2160,6 +2213,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -2179,6 +2233,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期（</t>
     </r>
@@ -2198,6 +2253,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -2217,6 +2273,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -2236,6 +2293,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">日）現在。単位：円（表示形式は千円）</t>
     </r>
@@ -2268,6 +2326,7 @@
         <color theme="0"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -2289,6 +2348,7 @@
         <color theme="0"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期</t>
     </r>
@@ -2312,6 +2372,7 @@
         <color theme="0"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -2333,6 +2394,7 @@
         <color theme="0"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期</t>
     </r>
@@ -2356,6 +2418,7 @@
         <color theme="0"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -2377,6 +2440,7 @@
         <color theme="0"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期</t>
     </r>
@@ -2491,6 +2555,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -2510,6 +2575,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期より取引開始</t>
     </r>
@@ -2534,6 +2600,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -2553,6 +2620,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期に増加</t>
     </r>
@@ -2631,6 +2699,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -2650,6 +2719,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期に増加。従前は販売先でもあった</t>
     </r>
@@ -2752,6 +2822,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -2771,6 +2842,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期 外注加工費</t>
     </r>
@@ -2790,6 +2862,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">千円のうち</t>
     </r>
@@ -2809,6 +2882,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">千円。関係会社（株）慈久庵伊勢又との関係整理が必要（要確認）</t>
     </r>
@@ -2870,6 +2944,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -2889,6 +2964,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -2908,6 +2984,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">日時点の登記簿（全部事項）に基づく。取締役会設置会社・監査役設置会社。役員報酬は</t>
     </r>
@@ -2927,6 +3004,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">期を通じて計上なし。</t>
     </r>
@@ -3127,6 +3205,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -3146,6 +3225,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -3167,6 +3247,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">階 店舗／</t>
     </r>
@@ -3186,6 +3267,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">階 代表者住居</t>
     </r>
@@ -3216,6 +3298,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -3235,6 +3318,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月〜</t>
     </r>
@@ -3254,6 +3338,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -3273,6 +3358,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -3303,6 +3389,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -3336,6 +3423,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -3355,6 +3443,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月〜</t>
     </r>
@@ -3374,6 +3463,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -3393,6 +3483,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -3423,6 +3514,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">番地</t>
     </r>
@@ -3454,6 +3546,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">階：</t>
     </r>
@@ -3474,6 +3567,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">階：</t>
     </r>
@@ -3494,6 +3588,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">合計：</t>
     </r>
@@ -3529,6 +3624,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -3548,6 +3644,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -3567,6 +3664,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">日新築</t>
     </r>
@@ -3633,6 +3731,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -3652,6 +3751,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -3671,6 +3771,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">日相続</t>
     </r>
@@ -3725,6 +3826,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">商事株式会社</t>
     </r>
@@ -3756,6 +3858,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -3773,6 +3876,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期 固定資産減価償却内訳明細書より主要資産を抜粋（</t>
     </r>
@@ -3790,6 +3894,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">〜</t>
     </r>
@@ -3807,6 +3912,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">）。</t>
     </r>
@@ -3824,6 +3930,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">〜</t>
     </r>
@@ -3841,6 +3948,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">は現地実査により把握した資産で、固定資産台帳との対応は要確認。取得価額合計</t>
     </r>
@@ -3858,6 +3966,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">千円、期末簿価合計</t>
     </r>
@@ -3875,6 +3984,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">千円。</t>
     </r>
@@ -3908,6 +4018,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -3927,6 +4038,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -3948,6 +4060,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">基</t>
     </r>
@@ -3972,6 +4085,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -3991,6 +4105,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期に取得。醤（ひしお）製造用</t>
     </r>
@@ -4018,6 +4133,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -4037,6 +4153,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -4058,6 +4175,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">台</t>
     </r>
@@ -4085,6 +4203,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -4104,6 +4223,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -4131,6 +4251,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -4150,6 +4271,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -4177,6 +4299,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -4196,6 +4319,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -4220,6 +4344,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -4239,6 +4364,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -4260,6 +4386,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">組</t>
     </r>
@@ -4284,6 +4411,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -4303,6 +4431,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -4324,6 +4453,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">式</t>
     </r>
@@ -4348,6 +4478,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -4367,6 +4498,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -4394,6 +4526,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -4413,6 +4546,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月〜</t>
     </r>
@@ -4432,6 +4566,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -4451,6 +4586,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -4472,6 +4608,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">台</t>
     </r>
@@ -4507,6 +4644,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -4528,6 +4666,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -4555,6 +4694,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -4574,6 +4714,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -4601,6 +4742,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -4620,6 +4762,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -4648,6 +4791,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">台</t>
     </r>
@@ -4676,6 +4820,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">台</t>
     </r>
@@ -4716,6 +4861,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">室</t>
     </r>
@@ -4741,6 +4887,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -4758,6 +4905,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月・</t>
     </r>
@@ -4775,6 +4923,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -4792,6 +4941,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -4830,6 +4980,7 @@
         <color rgb="FFFF0000"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">の財務詳細ページのデータは財務入力のシートから流用してください</t>
     </r>
@@ -5066,6 +5217,7 @@
         <color theme="0"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -5089,6 +5241,7 @@
         <color theme="0"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -5112,6 +5265,7 @@
         <color theme="0"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -5135,6 +5289,7 @@
         <color theme="0"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -5159,6 +5314,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">面談</t>
     </r>
@@ -5180,6 +5336,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ドラフト作成</t>
     </r>
@@ -5201,6 +5358,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">提出</t>
     </r>
@@ -5222,6 +5380,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">受領</t>
     </r>
@@ -5241,6 +5400,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">独占交渉権</t>
     </r>
@@ -5275,6 +5435,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">スコープ・依頼先選定</t>
     </r>
@@ -5296,6 +5457,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">提出</t>
     </r>
@@ -5317,6 +5479,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ラリー</t>
     </r>
@@ -5350,6 +5513,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">結果報告</t>
     </r>
@@ -5371,6 +5535,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">内容調整</t>
     </r>
@@ -5392,6 +5557,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">締結</t>
     </r>
@@ -5413,6 +5579,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">対応等</t>
     </r>
@@ -5447,6 +5614,7 @@
         <sz val="11"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">・グループ連携</t>
     </r>
@@ -5491,6 +5659,7 @@
         <color theme="0" tint="-0.05"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">承継機構</t>
     </r>
@@ -5512,6 +5681,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -5536,6 +5706,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">面談準備</t>
     </r>
@@ -5557,6 +5728,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">内容検討</t>
     </r>
@@ -5578,6 +5750,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ドラフト提示</t>
     </r>
@@ -5599,6 +5772,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">スコープ・依頼先検討</t>
     </r>
@@ -5620,6 +5794,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">回答</t>
     </r>
@@ -5639,6 +5814,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">独占交渉権付与</t>
     </r>
@@ -5673,6 +5849,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">内容説明</t>
     </r>
@@ -5694,6 +5871,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">スコープ・依頼先確定</t>
     </r>
@@ -5715,6 +5893,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">キックオフミーティング</t>
     </r>
@@ -5736,6 +5915,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">資料提出・</t>
     </r>
@@ -5755,6 +5935,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">対応</t>
     </r>
@@ -5776,6 +5957,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">提出※</t>
     </r>
@@ -5795,6 +5977,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">依頼先</t>
     </r>
@@ -5816,6 +5999,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">対応※</t>
     </r>
@@ -5835,6 +6019,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">依頼先</t>
     </r>
@@ -5856,6 +6041,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">マネジメントインタビュー</t>
     </r>
@@ -5877,6 +6063,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">内容検討</t>
     </r>
@@ -5898,6 +6085,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">ドラフト提出</t>
     </r>
@@ -5919,6 +6107,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">結果確認</t>
     </r>
@@ -5938,6 +6127,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">報告会</t>
     </r>
@@ -5969,6 +6159,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">案ご提出</t>
     </r>
@@ -5990,6 +6181,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">調整</t>
     </r>
@@ -6014,6 +6206,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">対応等</t>
     </r>
@@ -6041,6 +6234,7 @@
         <color theme="1"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -6062,6 +6256,7 @@
         <sz val="11"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">期 業績推移（決算書より直接転記。</t>
     </r>
@@ -6081,6 +6276,7 @@
         <sz val="11"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -6100,6 +6296,7 @@
         <sz val="11"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期・</t>
     </r>
@@ -6119,6 +6316,7 @@
         <sz val="11"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -6138,6 +6336,7 @@
         <sz val="11"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期は財務入力シート対象外）</t>
     </r>
@@ -6166,6 +6365,7 @@
         <sz val="8"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -6183,6 +6383,7 @@
         <sz val="8"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期〜</t>
     </r>
@@ -6200,6 +6401,7 @@
         <sz val="8"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -6217,6 +6419,7 @@
         <sz val="8"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期は </t>
     </r>
@@ -6234,6 +6437,7 @@
         <sz val="8"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">シートと一致。単位：円</t>
     </r>
@@ -6258,6 +6462,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -6277,6 +6482,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期</t>
     </r>
@@ -6298,6 +6504,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -6317,6 +6524,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期</t>
     </r>
@@ -6338,6 +6546,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -6357,6 +6566,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期</t>
     </r>
@@ -6378,6 +6588,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -6397,6 +6608,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期</t>
     </r>
@@ -6418,6 +6630,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -6437,6 +6650,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期</t>
     </r>
@@ -6479,6 +6693,7 @@
         <sz val="11"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">年</t>
     </r>
@@ -6498,6 +6713,7 @@
         <sz val="11"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月期 月次 店頭売上高・営業日数（総勘定元帳「飲食店売上高」の入金明細より集計）</t>
     </r>
@@ -6532,6 +6748,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -6551,6 +6768,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -6570,6 +6788,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -6589,6 +6808,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -6608,6 +6828,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -6627,6 +6848,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -6646,6 +6868,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -6665,6 +6888,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -6684,6 +6908,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -6703,6 +6928,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -6722,6 +6948,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -6741,6 +6968,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月</t>
     </r>
@@ -6760,6 +6988,7 @@
         <sz val="9"/>
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">月分現金売上（期末一括計上）</t>
     </r>
@@ -6828,7 +7057,7 @@
     <numFmt numFmtId="177" formatCode="#,##0"/>
     <numFmt numFmtId="178" formatCode="m\月d\日;@"/>
   </numFmts>
-  <fonts count="108">
+  <fonts count="96">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6928,20 +7157,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
@@ -6979,12 +7194,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="12"/>
       <color theme="1"/>
@@ -7012,6 +7221,7 @@
       <color rgb="FFFF0000"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
@@ -7039,6 +7249,7 @@
       <color rgb="FFC03A2B"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
@@ -7103,12 +7314,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="14"/>
       <color theme="1"/>
@@ -7134,11 +7339,6 @@
       <name val="游ゴシック Medium"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -7167,12 +7367,6 @@
       <name val="游ゴシック"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -7315,13 +7509,6 @@
       <b val="true"/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -7367,6 +7554,7 @@
       <color rgb="FFFF0000"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <b val="true"/>
@@ -7436,6 +7624,7 @@
       <color theme="0"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="8"/>
@@ -7475,11 +7664,6 @@
       <sz val="11"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -7501,13 +7685,6 @@
     <font>
       <b val="true"/>
       <sz val="11"/>
-      <color theme="0" tint="-0.05"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
       <name val="游ゴシック"/>
       <family val="0"/>
       <charset val="1"/>
@@ -7517,6 +7694,7 @@
       <sz val="11"/>
       <name val="WenQuanYi Zen Hei"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="8"/>
@@ -7525,28 +7703,10 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="8"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="9"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b val="true"/>
       <sz val="9"/>
       <name val="Arial"/>
       <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <name val="WenQuanYi Zen Hei"/>
-      <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
@@ -8946,2511 +9106,2511 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="3" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="3" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="3" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="9" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="9" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="2" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="16" fillId="2" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="3" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="3" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="16" fillId="2" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="2" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="16" fillId="2" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="3" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="2" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="16" fillId="2" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="16" fillId="2" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="28" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="28" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="29" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="29" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="29" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="31" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="31" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="31" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="31" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="3" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="3" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="3" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="4" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="4" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="2" borderId="28" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="28" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="25" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="8" borderId="28" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="6" fillId="8" borderId="28" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="24" fillId="5" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="21" fillId="5" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="10" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="10" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="10" borderId="33" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="10" borderId="33" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="10" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="10" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="10" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="10" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="3" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="26" fillId="0" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="27" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="27" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="18" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="35" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="36" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="36" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="30" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="27" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="37" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="37" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="37" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="37" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="37" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="37" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="17" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="15" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="9" borderId="37" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="9" borderId="37" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="9" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="9" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="9" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="9" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="16" fillId="2" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="2" borderId="38" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="16" fillId="2" borderId="38" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="5" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="5" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="5" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="5" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="40" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="40" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="5" borderId="41" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="5" borderId="41" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="42" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="42" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="36" fillId="9" borderId="42" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="33" fillId="9" borderId="42" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="37" fillId="9" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="34" fillId="9" borderId="43" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="44" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="44" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="45" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="45" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="5" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="5" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="5" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="5" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="46" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="46" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="46" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="5" borderId="46" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="5" borderId="46" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="36" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="33" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="11" fillId="0" borderId="40" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="36" fillId="9" borderId="42" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="33" fillId="9" borderId="42" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="42" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="42" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="23" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="20" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="23" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="20" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="23" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="20" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="23" fillId="5" borderId="40" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="20" fillId="5" borderId="40" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="9" borderId="42" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="9" borderId="42" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="48" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="48" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="49" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="49" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="50" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="50" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="16" fillId="2" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="2" borderId="51" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="16" fillId="2" borderId="51" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="52" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="52" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="36" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="36" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="53" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="54" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="54" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="55" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="55" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="4" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="36" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="36" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="3" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="38" fillId="5" borderId="53" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="35" fillId="5" borderId="53" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="54" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="54" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="55" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="55" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="3" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="16" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="2" borderId="56" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="16" fillId="2" borderId="56" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="57" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="57" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="2" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="16" fillId="2" borderId="26" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="18" fillId="2" borderId="58" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="16" fillId="2" borderId="58" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="9" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="5" borderId="53" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="5" borderId="53" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="38" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="35" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="16" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="14" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="5" borderId="59" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="5" borderId="59" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="10" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="10" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="16" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="14" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="38" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="35" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="10" fillId="5" borderId="40" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="10" fillId="5" borderId="40" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="9" borderId="42" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="9" borderId="42" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="4" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="14" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="40" fillId="9" borderId="42" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="36" fillId="9" borderId="42" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="60" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="60" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="40" fillId="9" borderId="61" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="36" fillId="9" borderId="61" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="62" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="62" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="63" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="63" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="37" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="51" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="51" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="8" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="38" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="38" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="55" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="55" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="27" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="60" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="60" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="36" fillId="3" borderId="65" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="33" fillId="3" borderId="65" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="36" fillId="3" borderId="61" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="33" fillId="3" borderId="61" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="42" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="42" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="9" borderId="42" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="9" borderId="42" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="42" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="42" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="9" borderId="66" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="9" borderId="66" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="66" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="66" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="36" fillId="9" borderId="66" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="33" fillId="9" borderId="66" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="9" borderId="33" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="9" borderId="33" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="9" borderId="33" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="9" borderId="33" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="36" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="172" fontId="33" fillId="9" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="42" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="38" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="43" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="39" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="45" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="40" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="42" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="38" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="46" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="41" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="47" fillId="2" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="42" fillId="2" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="48" fillId="2" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="43" fillId="2" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="50" fillId="2" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="44" fillId="2" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="50" fillId="8" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="44" fillId="8" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="45" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="46" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="53" fillId="4" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="47" fillId="4" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="54" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="48" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="36" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="36" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="55" fillId="0" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="49" fillId="0" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="36" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="36" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="56" fillId="0" borderId="36" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="50" fillId="0" borderId="36" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="36" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="56" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="50" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="56" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="50" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="56" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="50" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="57" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="51" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="57" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="51" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="67" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="67" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="68" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="68" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="69" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="69" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="33" fillId="0" borderId="69" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="69" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="47" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="42" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="70" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="70" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="4" borderId="70" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="70" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="16" fillId="0" borderId="71" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="71" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="23" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="4" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="4" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="4" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="72" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="72" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="72" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="72" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="30" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="63" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="57" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="50" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="41" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="45" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="40" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="3" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="57" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="51" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="46" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="41" fillId="5" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="50" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="56" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="50" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="40" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="4" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="40" fillId="4" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="3" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="57" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="51" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="4" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="4" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="23" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="20" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="61" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="55" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="64" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="58" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="11" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="11" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="11" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="11" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="5" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="174" fontId="11" fillId="5" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="174" fontId="11" fillId="5" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="11" fillId="5" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="11" fillId="5" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="38" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="35" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="5" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="5" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="4" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="5" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="5" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="5" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="5" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="10" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="10" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="5" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="176" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="66" fillId="2" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="60" fillId="2" borderId="47" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="66" fillId="2" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="60" fillId="2" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="56" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="50" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="10" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="10" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="176" fontId="10" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="45" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="40" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="50" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="45" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="40" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="67" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="176" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="50" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="176" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="45" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="40" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="56" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="50" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="16" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="38" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="35" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="10" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="10" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="11" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="16" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="5" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="5" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="16" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="14" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="176" fontId="38" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="176" fontId="35" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="63" fillId="2" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="57" fillId="2" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="6" fillId="2" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="6" fillId="2" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="56" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="50" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="40" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="45" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="40" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="56" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="50" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="56" fillId="4" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="50" fillId="4" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="45" fillId="0" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="40" fillId="0" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="56" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="50" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="5" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="56" fillId="3" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="50" fillId="3" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="57" fillId="3" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="51" fillId="3" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="8" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="69" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="62" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="70" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="63" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="71" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="177" fontId="64" fillId="4" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="72" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="65" fillId="0" borderId="64" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="71" fillId="4" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="177" fontId="64" fillId="4" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="72" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="65" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="42" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="38" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="72" fillId="0" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="65" fillId="0" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="71" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="177" fontId="64" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="71" fillId="3" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="177" fontId="64" fillId="3" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="3" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="38" fillId="3" borderId="34" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="42" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="38" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="73" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="66" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="74" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="67" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="35" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="32" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="69" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="78" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="71" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="79" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="72" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="80" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="73" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="81" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="74" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="177" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="82" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="75" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="76" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="84" fillId="2" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="77" fillId="2" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="86" fillId="2" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="79" fillId="2" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="87" fillId="12" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="80" fillId="12" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="175" fontId="88" fillId="13" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="175" fontId="81" fillId="13" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="89" fillId="4" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="82" fillId="4" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="20" fillId="0" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="18" fillId="0" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="82" fillId="6" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="75" fillId="6" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="82" fillId="5" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="75" fillId="5" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="87" fillId="5" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="80" fillId="5" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="59" fillId="4" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="53" fillId="4" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="90" fillId="6" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="83" fillId="6" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="82" fillId="0" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="75" fillId="0" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="87" fillId="5" borderId="74" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="80" fillId="5" borderId="74" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="20" fillId="12" borderId="74" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="18" fillId="12" borderId="74" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="20" fillId="13" borderId="74" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="18" fillId="13" borderId="74" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="93" fillId="2" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="85" fillId="2" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="93" fillId="2" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="85" fillId="2" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="94" fillId="2" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="86" fillId="2" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="20" fillId="7" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="18" fillId="7" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="4" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="4" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="14" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="14" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="20" fillId="12" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="18" fillId="12" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="20" fillId="13" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="18" fillId="13" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="178" fontId="20" fillId="4" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="178" fontId="18" fillId="4" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="61" fillId="4" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="55" fillId="4" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="73" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="80" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="73" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="79" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="72" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="71" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="177" fontId="64" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="177" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="80" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="73" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="177" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="177" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="177" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="77" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="70" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="72" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="75" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="75" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="76" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="76" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="5" borderId="76" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="5" borderId="76" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="77" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="77" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="78" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="78" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="34" fillId="5" borderId="79" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="31" fillId="5" borderId="79" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="39" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="80" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="80" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="9" fillId="3" borderId="81" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="9" fillId="3" borderId="81" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="71" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="71" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="82" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="82" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="9" fillId="3" borderId="83" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="9" fillId="3" borderId="83" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="84" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="84" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="79" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="79" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="9" fillId="3" borderId="85" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="9" fillId="3" borderId="85" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="86" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="86" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="9" fillId="3" borderId="87" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="9" fillId="3" borderId="87" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="88" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="88" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="89" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="89" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="9" fillId="3" borderId="90" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="9" fillId="3" borderId="90" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="91" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="91" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="9" fillId="3" borderId="92" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="9" fillId="3" borderId="92" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="69" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="69" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="93" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="93" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="94" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="94" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="9" fillId="0" borderId="95" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="9" fillId="0" borderId="95" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="9" fillId="0" borderId="96" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="9" fillId="0" borderId="96" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="97" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="97" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="173" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -11694,11 +11854,11 @@
         </c:ser>
         <c:gapWidth val="70"/>
         <c:overlap val="100"/>
-        <c:axId val="38154036"/>
-        <c:axId val="36574395"/>
+        <c:axId val="46513822"/>
+        <c:axId val="73618144"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="38154036"/>
+        <c:axId val="46513822"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11731,14 +11891,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36574395"/>
+        <c:crossAx val="73618144"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="36574395"/>
+        <c:axId val="73618144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11778,7 +11938,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38154036"/>
+        <c:crossAx val="46513822"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12092,11 +12252,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="39158859"/>
-        <c:axId val="11428730"/>
+        <c:axId val="10857240"/>
+        <c:axId val="35858835"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="39158859"/>
+        <c:axId val="10857240"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12129,7 +12289,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11428730"/>
+        <c:crossAx val="35858835"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12137,7 +12297,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="11428730"/>
+        <c:axId val="35858835"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12167,7 +12327,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39158859"/>
+        <c:crossAx val="10857240"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12575,11 +12735,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="27959162"/>
-        <c:axId val="66112527"/>
+        <c:axId val="52716234"/>
+        <c:axId val="64602919"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="27959162"/>
+        <c:axId val="52716234"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12612,7 +12772,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66112527"/>
+        <c:crossAx val="64602919"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12620,7 +12780,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="66112527"/>
+        <c:axId val="64602919"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12650,7 +12810,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="27959162"/>
+        <c:crossAx val="52716234"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12722,10 +12882,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.295793510683631"/>
-          <c:y val="0.15812976096664"/>
-          <c:w val="0.440920435867779"/>
-          <c:h val="0.734961912266877"/>
+          <c:x val="0.295750639230488"/>
+          <c:y val="0.158150531984763"/>
+          <c:w val="0.440886399610374"/>
+          <c:h val="0.734927098384343"/>
         </c:manualLayout>
       </c:layout>
       <c:doughnutChart>
@@ -13333,11 +13493,11 @@
         </c:ser>
         <c:gapWidth val="100"/>
         <c:overlap val="100"/>
-        <c:axId val="38641407"/>
-        <c:axId val="21626306"/>
+        <c:axId val="67369015"/>
+        <c:axId val="80627265"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="38641407"/>
+        <c:axId val="67369015"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13370,7 +13530,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21626306"/>
+        <c:crossAx val="80627265"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13378,7 +13538,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="21626306"/>
+        <c:axId val="80627265"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13408,7 +13568,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38641407"/>
+        <c:crossAx val="67369015"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13613,11 +13773,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="11050786"/>
-        <c:axId val="72162137"/>
+        <c:axId val="97132696"/>
+        <c:axId val="46984794"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="11050786"/>
+        <c:axId val="97132696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13650,7 +13810,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72162137"/>
+        <c:crossAx val="46984794"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13658,7 +13818,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="72162137"/>
+        <c:axId val="46984794"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13688,7 +13848,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11050786"/>
+        <c:crossAx val="97132696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13858,11 +14018,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="47530683"/>
-        <c:axId val="57415502"/>
+        <c:axId val="47562918"/>
+        <c:axId val="49373658"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="47530683"/>
+        <c:axId val="47562918"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13895,7 +14055,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="57415502"/>
+        <c:crossAx val="49373658"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13903,7 +14063,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="57415502"/>
+        <c:axId val="49373658"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13933,7 +14093,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="47530683"/>
+        <c:crossAx val="47562918"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13969,9 +14129,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>881640</xdr:colOff>
+      <xdr:colOff>881280</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>35640</xdr:rowOff>
+      <xdr:rowOff>35280</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -13980,7 +14140,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="2688120" y="2503440"/>
-        <a:ext cx="5678280" cy="3209040"/>
+        <a:ext cx="5677920" cy="3208680"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -14004,9 +14164,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>137160</xdr:colOff>
+      <xdr:colOff>136800</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>203760</xdr:rowOff>
+      <xdr:rowOff>203400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -14015,7 +14175,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="9451080" y="206280"/>
-        <a:ext cx="5897520" cy="2740680"/>
+        <a:ext cx="5897160" cy="2740320"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -14034,9 +14194,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>165960</xdr:colOff>
+      <xdr:colOff>165600</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>172080</xdr:rowOff>
+      <xdr:rowOff>171720</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -14045,7 +14205,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="9464040" y="3832200"/>
-        <a:ext cx="5913360" cy="2740680"/>
+        <a:ext cx="5913000" cy="2740320"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -14064,9 +14224,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>172080</xdr:colOff>
+      <xdr:colOff>171720</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>178560</xdr:rowOff>
+      <xdr:rowOff>178200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -14075,7 +14235,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="9470160" y="7267680"/>
-        <a:ext cx="5913360" cy="2740680"/>
+        <a:ext cx="5913000" cy="2740320"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -14094,9 +14254,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>310680</xdr:colOff>
+      <xdr:colOff>310320</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>39960</xdr:rowOff>
+      <xdr:rowOff>39600</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -14105,7 +14265,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="9621360" y="10993680"/>
-        <a:ext cx="5900760" cy="2762280"/>
+        <a:ext cx="5900400" cy="2761920"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -14124,9 +14284,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>137160</xdr:colOff>
+      <xdr:colOff>136800</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>203760</xdr:rowOff>
+      <xdr:rowOff>203400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -14135,7 +14295,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="21569760" y="206280"/>
-        <a:ext cx="5313600" cy="2740680"/>
+        <a:ext cx="5313240" cy="2740320"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -14154,9 +14314,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>137160</xdr:colOff>
+      <xdr:colOff>136800</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>203760</xdr:rowOff>
+      <xdr:rowOff>203400</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -14165,7 +14325,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="21569760" y="4092480"/>
-        <a:ext cx="5313600" cy="2740680"/>
+        <a:ext cx="5313240" cy="2740320"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
